--- a/reports/whatsapp_report.xlsx
+++ b/reports/whatsapp_report.xlsx
@@ -422,8 +422,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="41" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" min="10" max="10"/>
   </cols>
@@ -503,7 +503,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:29</t>
+          <t>2026-08-26 22:41:42</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -512,20 +512,21 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>3:54 pm</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>Hello loganathan, how are you?
 9:50 pm</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Hello loganathan, how are you?
 10:15 pm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Hello loganathan, how are you?
+10:41 pm</t>
         </is>
       </c>
     </row>
@@ -552,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-26 22:16:00</t>
+          <t>2026-08-26 22:42:10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
